--- a/data_extactor/batch_10_fa/trimmed/batch_0034_fa_trim.xlsx
+++ b/data_extactor/batch_10_fa/trimmed/batch_0034_fa_trim.xlsx
@@ -508,12 +508,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>درک مطلب | شنیدن فعال | سخن گفتن | نگارش | تفکر انتقادی | راهبردهای یادگیری | یادگیری فعال | نظارت</t>
+          <t>درک مطلب | گوش دادن فعال | سخن گفتن | نگارش | تفکر انتقادی | راهبردهای یادگیری | یادگیری فعال | نظارت</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>فلسفه و الهیات | زبان انگلیسی | آموزش و تدریس | تاریخ و باستان‌شناسی | جامعه‌شناسی و مردم‌شناسی | حقوق و امور دولتی</t>
+          <t>فلسفه و الهیات | زبان انگلیسی | آموزش و پرورش | تاریخ و باستان‌شناسی | جامعه‌شناسی و انسان‌شناسی | قانون و دولت</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>مدرسان مردم‌شناسی و باستان‌شناسی در آموزش عالی | مدرسان مطالعات منطقه‌ای، قومیتی و فرهنگی در آموزش عالی | مدرسان زبان و ادبیات انگلیسی در آموزش عالی | مدرسان تاریخ در آموزش عالی | مدرسان حقوق در آموزش عالی | مدرسان علوم سیاسی در آموزش عالی | مدرسان جامعه‌شناسی در آموزش عالی</t>
+          <t>استادان انسان‌شناسی و باستان‌شناسی دانشگاه | استادان مطالعات منطقه‌ای، قومی و فرهنگی دانشگاه | مدرسان زبان و ادبیات انگلیسی در دانشگاه‌ها و مراکز آموزش عالی | مدرسان تاریخ در دانشگاه‌ها و مراکز آموزش عالی | مدرسان حقوق در دانشگاه‌ها و مراکز آموزش عالی | استادان علوم سیاسی دانشگاه | استادان جامعه‌شناسی دانشگاه</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,12 +565,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>سخن گفتن | راهبردهای یادگیری | شنیدن فعال | درک مطلب | تفکر انتقادی | نگارش | یادگیری فعال | نظارت</t>
+          <t>سخن گفتن | راهبردهای یادگیری | گوش دادن فعال | درک مطلب | تفکر انتقادی | نگارش | یادگیری فعال | نظارت</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>آموزش و تدریس | خدمات مشتریان و خدمات فردی | روان‌شناسی | مدیریت و امور اداری | ریاضیات | جامعه‌شناسی و مردم‌شناسی</t>
+          <t>آموزش و پرورش | خدمات مشتری و شخصی | روان‌شناسی | مدیریت و اداره | ریاضیات | جامعه‌شناسی و انسان‌شناسی</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>مدرسان علوم دامی و کشاورزی در آموزش عالی | مدرسان علوم تربیتی در آموزش عالی | کارشناسان آموزش سلامت و بهداشت | هماهنگ‌کنندگان و کارشناسان برنامه‌ریزی درسی | مدرسان روان‌شناسی در آموزش عالی | مدرسان مددکاری اجتماعی در آموزش عالی | مدرسان جامعه‌شناسی در آموزش عالی</t>
+          <t>استادان و مدرسان علوم کشاورزی در دانشگاه‌ها و مراکز آموزش عالی | مدرسان علوم تربیتی و آموزش در دانشگاه‌ها و مراکز آموزش عالی | کارشناسان آموزش بهداشت و ارتقای سلامت | کارشناسان و هماهنگ‌کنندگان برنامه‌ریزی درسی و آموزشی | استادان روان‌شناسی دانشگاه | مدرسان مددکاری اجتماعی در دانشگاه‌ها و مراکز آموزش عالی | استادان جامعه‌شناسی دانشگاه</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,12 +622,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>سخن گفتن | نگارش | شنیدن فعال | درک مطلب | راهبردهای یادگیری | تفکر انتقادی | نظارت | یادگیری فعال</t>
+          <t>سخن گفتن | نگارش | گوش دادن فعال | درک مطلب | راهبردهای یادگیری | تفکر انتقادی | نظارت | یادگیری فعال</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>آموزش و تدریس | روان‌شناسی | زیست‌شناسی | خدمات مشتریان و خدمات فردی | مدیریت و امور اداری | پزشکی و دندان‌پزشکی</t>
+          <t>آموزش و پرورش | روان‌شناسی | زیست‌شناسی | خدمات مشتری و شخصی | مدیریت و اداره | پزشکی و دندان‌پزشکی</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>کارشناسان تربیت بدنی انطباقی و استثنایی | مدرسان علوم زیستی در آموزش عالی | مدرسان علوم تربیتی در آموزش عالی | کارشناسان برنامه‌ریزی تندرستی و سلامت | مدرسان علوم و تخصص‌های پیراپزشکی در آموزش عالی | مدرسان و مربیان پرستاری در آموزش عالی | مدرسان دوره‌های آزاد و مهارت‌های فردی</t>
+          <t>متخصصان تربیت بدنی انطباقی | استادان و مدرسان علوم زیستی در دانشگاه‌ها و مراکز آموزش عالی | مدرسان علوم تربیتی و آموزش در دانشگاه‌ها و مراکز آموزش عالی | مدیران و هماهنگ‌کننده‌های برنامه‌های سلامت و تندرستی | استادان تخصص‌های علوم پزشکی و بهداشت دانشگاه | مربیان و استادان پرستاری دانشگاه | مربیان دوره‌های آزاد و مهارت‌آموزی فردی</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,12 +679,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>راهبردهای یادگیری | شنیدن فعال | درک مطلب | سخن گفتن | یادگیری فعال | تفکر انتقادی | نگارش | نظارت</t>
+          <t>راهبردهای یادگیری | گوش دادن فعال | درک مطلب | سخن گفتن | یادگیری فعال | تفکر انتقادی | نگارش | نظارت</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>آموزش و تدریس | مکانیک | ریاضیات | مهندسی و فناوری | رایانه و الکترونیک | ایمنی و امنیت عمومی</t>
+          <t>آموزش و پرورش | مکانیک | ریاضیات | مهندسی و فناوری | رایانه و الکترونیک | ایمنی و امنیت عمومی</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>کاردان‌ها و تکنسین‌های مهندسی خودرو | معلمان آموزش فنی‌وحرفه‌ای دوره اول متوسطه | معلمان آموزش فنی‌وحرفه‌ای دوره دوم متوسطه | کاردان‌ها و تکنسین‌های مهندسی صنایع | کاردان‌ها و تکنسین‌های مهندسی مکانیک | مدرسان دوره‌های آزاد و مهارت‌های فردی | کارشناسان آموزش و توانمندسازی منابع انسانی</t>
+          <t>تکنسین‌های مهندسی خودرو | معلمان آموزش‌های فنی و حرفه‌ای در دوره اول متوسطه | هنرآموزان و معلمان فنی‌وحرفه‌ای و کاردانش دوره دوم متوسطه | کارشناسان و تکنسین‌های مهندسی صنایع | کارشناسان و تکنسین‌های مهندسی مکانیک | مربیان دوره‌های آزاد و مهارت‌آموزی فردی | کارشناسان آموزش و توسعه منابع انسانی</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,12 +736,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>سخن گفتن | شنیدن فعال | درک مطلب | تفکر انتقادی | راهبردهای یادگیری | نگارش | یادگیری فعال | نظارت</t>
+          <t>سخن گفتن | گوش دادن فعال | درک مطلب | تفکر انتقادی | راهبردهای یادگیری | نگارش | یادگیری فعال | نظارت</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>آموزش و تدریس | ارتباطات و رسانه | رایانه و الکترونیک | روان‌شناسی | مدیریت و امور اداری | ریاضیات</t>
+          <t>آموزش و پرورش | ارتباطات و رسانه | رایانه و الکترونیک | روان‌شناسی | مدیریت و اداره | ریاضیات</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>مدرسان علوم تربیتی در آموزش عالی | مدرسان علوم ارتباطات در آموزش عالی | مدرسان آموزش فنی‌وحرفه‌ای در آموزش عالی | سایر مدرسان علوم اجتماعی در آموزش عالی | هماهنگ‌کنندگان و کارشناسان برنامه‌ریزی درسی | مدیران امور آموزشی دانشگاه‌ها و مؤسسات آموزش عالی | مدرسان دوره‌های آزاد و مهارت‌های فردی</t>
+          <t>مدرسان علوم تربیتی و آموزش در دانشگاه‌ها و مراکز آموزش عالی | مدرسان علوم ارتباطات در دانشگاه‌ها و مراکز آموزش عالی | مدرسان آموزش‌های فنی و حرفه‌ای در آموزش عالی | سایر استادان علوم اجتماعی دانشگاه | کارشناسان و هماهنگ‌کنندگان برنامه‌ریزی درسی و آموزشی | مدیران آموزش عالی | مربیان دوره‌های آزاد و مهارت‌آموزی فردی</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,17 +793,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>سخن گفتن | راهبردهای یادگیری | شنیدن فعال | تفکر انتقادی | نظارت | درک مطلب | یادگیری فعال | نگارش</t>
+          <t>سخن گفتن | راهبردهای یادگیری | گوش دادن فعال | تفکر انتقادی | نظارت | درک مطلب | یادگیری فعال | نگارش</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>آموزش و تدریس | زبان انگلیسی | ایمنی و امنیت عمومی | خدمات مشتریان و خدمات فردی | روان‌شناسی</t>
+          <t>آموزش و پرورش | زبان انگلیسی | ایمنی و امنیت عمومی | خدمات مشتری و شخصی | روان‌شناسی</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | حساسیت به مسئله | ابتکار و خلاقیت | روانی بیان ایده‌ها | درک کتبی</t>
+          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | حساسیت به مسئله | اصالت | روانی ایده‌ها | درک کتبی</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>مربیان نگهداری کودک | مدیران مهدهای کودک و مراکز پیش‌دبستانی | معلمان دوره ابتدایی، به‌جز آموزش استثنایی | هماهنگ‌کنندگان و کارشناسان برنامه‌ریزی درسی | معلمان دوره پیش‌دبستانی و آمادگی، به‌جز آموزش استثنایی | معلمان آموزش استثنایی دوره پیش‌دبستانی و کودکستان | مربیان آموزشی مدارس ابتدایی و متوسطه، به‌جز استثنایی</t>
+          <t>مربیان و مراقبان کودک | مدیران مراکز آموزشی و مراقبت از کودک، پیش‌دبستانی و مهدکودک | معلمان دوره ابتدایی، به‌جز آموزش استثنایی | کارشناسان و هماهنگ‌کنندگان برنامه‌ریزی درسی و آموزشی | معلمان دوره پیش‌دبستانی و آمادگی، به‌جز آموزش استثنایی | معلمان آموزش استثنایی دوره آمادگی و نوآموزان | کمک‌معلمان دوره‌های پیش‌دبستانی، ابتدایی، دوره اول و دوم متوسطه (به‌جز آموزش استثنایی)</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,17 +850,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>نظارت | راهبردهای یادگیری | سخن گفتن | شنیدن فعال | درک مطلب | یادگیری فعال | تفکر انتقادی | نگارش</t>
+          <t>نظارت | راهبردهای یادگیری | سخن گفتن | گوش دادن فعال | درک مطلب | یادگیری فعال | تفکر انتقادی | نگارش</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>آموزش و تدریس | روان‌شناسی | ریاضیات | خدمات مشتریان و خدمات فردی | ایمنی و امنیت عمومی | درمان و مشاوره</t>
+          <t>آموزش و پرورش | روان‌شناسی | ریاضیات | خدمات مشتری و شخصی | ایمنی و امنیت عمومی | درمان و مشاوره</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک کتبی | درک شفاهی | بیان کتبی | حساسیت به مسئله | وضوح گفتار | روانی بیان ایده‌ها</t>
+          <t>بیان شفاهی | درک کتبی | درک شفاهی | بیان کتبی | حساسیت به مسئله | وضوح گفتار | روانی ایده‌ها</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>مدرسان علوم تربیتی در آموزش عالی | مدیران مهدهای کودک و مراکز پیش‌دبستانی | معلمان دوره ابتدایی، به‌جز آموزش استثنایی | هماهنگ‌کنندگان و کارشناسان برنامه‌ریزی درسی | مربیان پیش‌دبستانی و مهدکودک، به‌جز آموزش استثنایی | روان‌شناسان مدرسه | معلمان آموزش استثنایی دوره پیش‌دبستانی و کودکستان</t>
+          <t>مدرسان علوم تربیتی و آموزش در دانشگاه‌ها و مراکز آموزش عالی | مدیران مراکز آموزشی و مراقبت از کودک، پیش‌دبستانی و مهدکودک | معلمان دوره ابتدایی، به‌جز آموزش استثنایی | کارشناسان و هماهنگ‌کنندگان برنامه‌ریزی درسی و آموزشی | مربیان پیش‌دبستانی و مهدکودک، به‌جز آموزش استثنایی | روان‌شناسان مدارس | معلمان آموزش استثنایی دوره آمادگی و نوآموزان</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,12 +907,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>راهبردهای یادگیری | سخن گفتن | شنیدن فعال | نظارت | تفکر انتقادی | درک مطلب | نگارش | یادگیری فعال</t>
+          <t>راهبردهای یادگیری | سخن گفتن | گوش دادن فعال | نظارت | تفکر انتقادی | درک مطلب | نگارش | یادگیری فعال</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>آموزش و تدریس | ریاضیات | خدمات مشتریان و خدمات فردی | روان‌شناسی | درمان و مشاوره | رایانه و الکترونیک</t>
+          <t>آموزش و پرورش | ریاضیات | خدمات مشتری و شخصی | روان‌شناسی | درمان و مشاوره | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>مدیران مدارس ابتدایی و متوسطه | مدرسان علوم تربیتی در آموزش عالی | هماهنگ‌کنندگان و کارشناسان برنامه‌ریزی درسی | معلمان دوره پیش‌دبستانی و آمادگی، به‌جز آموزش استثنایی | معلمان دوره اول متوسطه، به‌جز آموزش استثنایی و فنی‌وحرفه‌ای | معلمان آموزش استثنایی دوره ابتدایی | مربیان آموزشی مدارس ابتدایی و متوسطه، به‌جز استثنایی</t>
+          <t>مدیران آموزشی مقاطع ابتدایی و متوسطه | مدرسان علوم تربیتی و آموزش در دانشگاه‌ها و مراکز آموزش عالی | کارشناسان و هماهنگ‌کنندگان برنامه‌ریزی درسی و آموزشی | معلمان دوره پیش‌دبستانی و آمادگی، به‌جز آموزش استثنایی | معلمان دوره اول متوسطه، به‌جز آموزش استثنایی و فنی‌وحرفه‌ای | معلمان آموزش استثنایی دوره ابتدایی | کمک‌معلمان دوره‌های پیش‌دبستانی، ابتدایی، دوره اول و دوم متوسطه (به‌جز آموزش استثنایی)</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,17 +964,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>راهبردهای یادگیری | سخن گفتن | شنیدن فعال | درک مطلب | نگارش | یادگیری فعال | نظارت | تفکر انتقادی</t>
+          <t>راهبردهای یادگیری | سخن گفتن | گوش دادن فعال | درک مطلب | نگارش | یادگیری فعال | نظارت | تفکر انتقادی</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>آموزش و تدریس | فلسفه و الهیات | ریاضیات | روان‌شناسی | رایانه و الکترونیک | تاریخ و باستان‌شناسی</t>
+          <t>آموزش و پرورش | فلسفه و الهیات | ریاضیات | روان‌شناسی | رایانه و الکترونیک | تاریخ و باستان‌شناسی</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک شفاهی | درک کتبی | بیان کتبی | حساسیت به مسئله | مرتب‌سازی اطلاعات | استدلال قیاسی</t>
+          <t>بیان شفاهی | درک شفاهی | درک کتبی | بیان کتبی | حساسیت به مسئله | ترتیب‌دهی اطلاعات | استدلال قیاسی</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>معلمان آموزش فنی‌وحرفه‌ای دوره اول متوسطه | مدیران مدارس ابتدایی و متوسطه | مدرسان علوم تربیتی در آموزش عالی | معلمان دوره ابتدایی، به‌جز آموزش استثنایی | هماهنگ‌کنندگان و کارشناسان برنامه‌ریزی درسی | معلمان دوره دوم متوسطه، به‌جز آموزش استثنایی و فنی‌وحرفه‌ای | معلمان آموزش استثنایی دوره اول متوسطه</t>
+          <t>معلمان آموزش‌های فنی و حرفه‌ای در دوره اول متوسطه | مدیران آموزشی مقاطع ابتدایی و متوسطه | مدرسان علوم تربیتی و آموزش در دانشگاه‌ها و مراکز آموزش عالی | معلمان دوره ابتدایی، به‌جز آموزش استثنایی | کارشناسان و هماهنگ‌کنندگان برنامه‌ریزی درسی و آموزشی | دبیران دوره دوم متوسطه، به‌جز آموزش استثنایی و فنی‌وحرفه‌ای | معلمان آموزش استثنایی دوره اول متوسطه</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,12 +1021,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>سخن گفتن | شنیدن فعال | درک مطلب | راهبردهای یادگیری | تفکر انتقادی | نظارت | نگارش | یادگیری فعال</t>
+          <t>سخن گفتن | گوش دادن فعال | درک مطلب | راهبردهای یادگیری | تفکر انتقادی | نظارت | نگارش | یادگیری فعال</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>آموزش و تدریس | روان‌شناسی | رایانه و الکترونیک | مدیریت و امور اداری | مهندسی و فناوری | ایمنی و امنیت عمومی</t>
+          <t>آموزش و پرورش | روان‌شناسی | رایانه و الکترونیک | مدیریت و اداره | مهندسی و فناوری | ایمنی و امنیت عمومی</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>مدرسان آموزش فنی‌وحرفه‌ای در آموزش عالی | معلمان آموزش فنی‌وحرفه‌ای دوره دوم متوسطه | مدیران مدارس ابتدایی و متوسطه | مشاوران و کارشناسان هدایت تحصیلی و شغلی | هماهنگ‌کنندگان و کارشناسان برنامه‌ریزی درسی | معلمان دوره اول متوسطه، به‌جز آموزش استثنایی و فنی‌وحرفه‌ای | مربیان آموزشی مدارس ابتدایی و متوسطه، به‌جز استثنایی</t>
+          <t>مدرسان آموزش‌های فنی و حرفه‌ای در آموزش عالی | هنرآموزان و معلمان فنی‌وحرفه‌ای و کاردانش دوره دوم متوسطه | مدیران آموزشی مقاطع ابتدایی و متوسطه | مشاوران تحصیلی، شغلی و هدایت استعدادها | کارشناسان و هماهنگ‌کنندگان برنامه‌ریزی درسی و آموزشی | معلمان دوره اول متوسطه، به‌جز آموزش استثنایی و فنی‌وحرفه‌ای | کمک‌معلمان دوره‌های پیش‌دبستانی، ابتدایی، دوره اول و دوم متوسطه (به‌جز آموزش استثنایی)</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
